--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T09:05:22+00:00</t>
+    <t>2024-04-25T09:06:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-16T08:04:49+00:00</t>
+    <t>2024-05-23T12:00:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.1</t>
+    <t>3.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:00:22+00:00</t>
+    <t>2024-06-05T13:15:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T13:15:20+00:00</t>
+    <t>2024-06-05T13:17:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T13:17:40+00:00</t>
+    <t>2024-06-17T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-17T15:07:22+00:00</t>
+    <t>2024-07-01T14:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T13:41:42+00:00</t>
+    <t>2025-02-27T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T09:48:09+00:00</t>
+    <t>2025-03-04T08:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:17:54+00:00</t>
+    <t>2025-03-06T14:47:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:47:34+00:00</t>
+    <t>2025-03-07T13:06:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:06:03+00:00</t>
+    <t>2025-04-23T14:15:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2488,17 +2488,17 @@
   <dimension ref="A1:AP117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="51.58984375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="44.2265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.26953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="223.14453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2507,28 +2507,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="111.65625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="95.7265625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T14:15:06+00:00</t>
+    <t>2025-05-21T14:32:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:16+00:00</t>
+    <t>2025-07-21T12:31:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-21T12:31:31+00:00</t>
+    <t>2025-10-13T07:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4813,7 +4813,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>207</v>
       </c>
@@ -5535,7 +5535,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>249</v>
       </c>
@@ -5775,7 +5775,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>272</v>
       </c>
@@ -6137,7 +6137,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>278</v>
       </c>
@@ -6497,7 +6497,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>291</v>
       </c>
@@ -6739,7 +6739,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>309</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>345</v>
       </c>
@@ -8791,7 +8791,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>382</v>
       </c>
@@ -9155,7 +9155,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>409</v>
       </c>
@@ -9637,7 +9637,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>450</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>457</v>
       </c>
@@ -10243,7 +10243,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>478</v>
       </c>
@@ -10363,7 +10363,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>486</v>
       </c>
@@ -10483,7 +10483,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>495</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>504</v>
       </c>
@@ -13735,7 +13735,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>563</v>
       </c>
@@ -13975,7 +13975,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>580</v>
       </c>
@@ -15535,7 +15535,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
         <v>655</v>
       </c>
@@ -16017,7 +16017,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
         <v>665</v>
       </c>
@@ -16139,7 +16139,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
         <v>671</v>
       </c>
@@ -16261,7 +16261,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>680</v>
       </c>
@@ -16629,12 +16629,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP117">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$117</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$118</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4511" uniqueCount="690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4549" uniqueCount="695">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T07:29:09+00:00</t>
+    <t>2025-10-13T07:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,7 +676,7 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
   </si>
   <si>
     <t>Observation.extension:MesReasonForMeasurement</t>
@@ -692,7 +692,24 @@
     <t>Motif de la mesure</t>
   </si>
   <si>
-    <t>Extension du Motif de la mesure, exprimé en texte libre  (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…).</t>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -1353,7 +1370,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|PractitionerRole)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2485,7 +2502,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP117"/>
+  <dimension ref="A1:AP118"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.2265625" customWidth="true" bestFit="true"/>
@@ -2498,7 +2515,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="179.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -5058,43 +5075,41 @@
         <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="C22" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="D22" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>114</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>220</v>
-      </c>
+        <v>221</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -5142,7 +5157,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5166,7 +5181,7 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5184,7 +5199,7 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5197,23 +5212,25 @@
         <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O23" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="N23" s="2"/>
-      <c r="O23" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5262,7 +5279,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5274,22 +5291,22 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>227</v>
+        <v>82</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>228</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>230</v>
+        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -5297,14 +5314,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5323,17 +5340,17 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5382,7 +5399,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5397,19 +5414,19 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5417,14 +5434,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5443,18 +5460,18 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5502,7 +5519,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5517,16 +5534,16 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5535,48 +5552,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>173</v>
+        <v>247</v>
       </c>
       <c r="L26" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5600,11 +5615,13 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>255</v>
+        <v>82</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5622,13 +5639,13 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -5637,30 +5654,30 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>257</v>
+        <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>260</v>
+        <v>82</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5671,31 +5688,31 @@
         <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5720,35 +5737,35 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y27" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y27" s="2"/>
       <c r="Z27" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AC27" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5757,34 +5774,32 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>82</v>
+        <v>262</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>82</v>
+        <v>263</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>273</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5793,7 +5808,7 @@
         <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>94</v>
@@ -5805,19 +5820,19 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5845,28 +5860,26 @@
         <v>177</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="AC28" s="2"/>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5890,35 +5903,37 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>266</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
@@ -5927,16 +5942,20 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>108</v>
+        <v>268</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
+        <v>269</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>271</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5960,13 +5979,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -5984,19 +6003,19 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>110</v>
+        <v>266</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -6008,10 +6027,10 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>111</v>
+        <v>275</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>82</v>
+        <v>276</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -6019,21 +6038,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -6045,17 +6064,15 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -6092,31 +6109,31 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6137,48 +6154,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>280</v>
+        <v>115</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>281</v>
+        <v>116</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6214,19 +6229,19 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>121</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6238,7 +6253,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6247,10 +6262,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>286</v>
+        <v>111</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6259,12 +6274,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6272,31 +6287,35 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>108</v>
+        <v>285</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6344,19 +6363,19 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>110</v>
+        <v>289</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6365,10 +6384,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>111</v>
+        <v>291</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6379,21 +6398,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6405,17 +6424,15 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6452,31 +6469,31 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6497,134 +6514,132 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>293</v>
+        <v>115</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>294</v>
+        <v>116</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP34" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>297</v>
-      </c>
-      <c r="S34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF34" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AG34" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH34" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ34" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" hidden="true">
-      <c r="A35" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6632,13 +6647,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6647,24 +6662,26 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>302</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6706,7 +6723,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6727,24 +6744,24 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AN35" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AO35" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP35" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" hidden="true">
+      <c r="A36" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>307</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AO35" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP35" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6752,13 +6769,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6767,24 +6784,24 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6826,7 +6843,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6847,10 +6864,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6859,12 +6876,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6872,13 +6889,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6887,24 +6904,24 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6946,7 +6963,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6967,10 +6984,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6981,10 +6998,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7007,19 +7024,17 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>328</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7068,7 +7083,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7089,10 +7104,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7103,10 +7118,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7129,19 +7144,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>333</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7190,7 +7205,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7211,10 +7226,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7223,26 +7238,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
@@ -7251,19 +7266,19 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>262</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7288,13 +7303,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7312,10 +7327,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>93</v>
@@ -7327,62 +7342,66 @@
         <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>108</v>
+        <v>352</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7406,13 +7425,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7430,10 +7449,10 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>110</v>
+        <v>350</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>93</v>
@@ -7442,44 +7461,44 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>82</v>
+        <v>359</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>82</v>
+        <v>360</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>111</v>
+        <v>361</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7491,17 +7510,15 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7538,31 +7555,31 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7585,18 +7602,18 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>81</v>
@@ -7608,23 +7625,21 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>280</v>
+        <v>115</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>281</v>
+        <v>116</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7660,9 +7675,11 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7670,7 +7687,7 @@
         <v>120</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>284</v>
+        <v>121</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7682,7 +7699,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7691,10 +7708,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>286</v>
+        <v>111</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7705,14 +7722,12 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>366</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7721,7 +7736,7 @@
         <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7736,16 +7751,16 @@
         <v>151</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7782,19 +7797,17 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7815,10 +7828,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7829,18 +7842,20 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="C45" s="2"/>
+      <c r="C45" t="s" s="2">
+        <v>369</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>93</v>
@@ -7852,19 +7867,23 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>108</v>
+        <v>285</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7912,19 +7931,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>110</v>
+        <v>289</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7933,10 +7952,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>111</v>
+        <v>291</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7947,21 +7966,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7973,17 +7992,15 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -8020,31 +8037,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -8067,21 +8084,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -8090,29 +8107,27 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>293</v>
+        <v>115</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>294</v>
+        <v>116</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>371</v>
+        <v>82</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -8142,31 +8157,31 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>298</v>
+        <v>121</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8175,10 +8190,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>300</v>
+        <v>111</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8189,10 +8204,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8200,7 +8215,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8215,24 +8230,26 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8274,7 +8291,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8295,10 +8312,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8309,10 +8326,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8320,7 +8337,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -8335,24 +8352,24 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8394,7 +8411,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8415,10 +8432,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8429,10 +8446,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8440,7 +8457,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -8455,24 +8472,24 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>82</v>
+        <v>381</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>82</v>
@@ -8514,7 +8531,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8535,10 +8552,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8549,10 +8566,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8575,19 +8592,17 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>328</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8636,7 +8651,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8657,10 +8672,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8671,10 +8686,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8697,19 +8712,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>333</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8758,7 +8773,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8779,10 +8794,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8791,12 +8806,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8804,13 +8819,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8819,19 +8834,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>383</v>
+        <v>107</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>385</v>
+        <v>344</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>386</v>
+        <v>345</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>387</v>
+        <v>346</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8880,7 +8895,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>382</v>
+        <v>347</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8895,30 +8910,30 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>388</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>389</v>
+        <v>348</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>390</v>
+        <v>349</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>391</v>
+        <v>82</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8926,13 +8941,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -8941,18 +8956,20 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -9000,13 +9017,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -9015,19 +9032,19 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>355</v>
+        <v>394</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9035,21 +9052,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -9061,20 +9078,18 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="M55" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>404</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9122,13 +9137,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -9137,44 +9152,44 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>406</v>
+        <v>360</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>410</v>
+        <v>404</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9183,19 +9198,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9244,7 +9259,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9253,50 +9268,50 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>417</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
@@ -9305,18 +9320,20 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>129</v>
+        <v>416</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9364,34 +9381,34 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
         <v>422</v>
       </c>
-      <c r="AG57" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>105</v>
-      </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AO57" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9399,10 +9416,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9413,7 +9430,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9425,18 +9442,18 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="L58" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>433</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9484,13 +9501,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9499,19 +9516,19 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>434</v>
+        <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9519,10 +9536,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9533,10 +9550,10 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
@@ -9545,19 +9562,17 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9594,59 +9609,59 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AC59" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>448</v>
+        <v>441</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>82</v>
+        <v>442</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>450</v>
+        <v>443</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9667,19 +9682,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9689,7 +9704,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9716,19 +9731,17 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="AC60" s="2"/>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9737,7 +9750,7 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9746,29 +9759,31 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>443</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9780,25 +9795,29 @@
         <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>107</v>
+        <v>444</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>108</v>
+        <v>445</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>445</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>447</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9807,7 +9826,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>82</v>
+        <v>457</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>82</v>
@@ -9846,7 +9865,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>110</v>
+        <v>443</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9855,47 +9874,47 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>111</v>
+        <v>453</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>82</v>
+        <v>454</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9907,17 +9926,15 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9954,31 +9971,31 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9999,48 +10016,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>459</v>
+        <v>114</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>460</v>
+        <v>115</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>461</v>
+        <v>116</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10076,31 +10091,31 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>464</v>
+        <v>121</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10109,10 +10124,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>466</v>
+        <v>111</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10121,12 +10136,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10134,83 +10149,83 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>173</v>
+        <v>464</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="P64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q64" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="R64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X64" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y64" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10231,10 +10246,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10243,12 +10258,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>479</v>
+        <v>473</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10256,37 +10271,39 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q65" s="2"/>
+      <c r="Q65" t="s" s="2">
+        <v>477</v>
+      </c>
       <c r="R65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10306,13 +10323,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>82</v>
+        <v>478</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>82</v>
+        <v>479</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10330,7 +10347,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10351,10 +10368,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10365,10 +10382,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10391,24 +10408,24 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>491</v>
+        <v>82</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>82</v>
@@ -10450,7 +10467,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10459,7 +10476,7 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10471,10 +10488,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10485,10 +10502,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10511,26 +10528,24 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>494</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>82</v>
@@ -10548,13 +10563,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>500</v>
+        <v>82</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10572,7 +10587,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10581,7 +10596,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>498</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10593,10 +10608,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10607,10 +10622,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10618,7 +10633,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>93</v>
@@ -10630,22 +10645,22 @@
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>262</v>
+        <v>173</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10670,13 +10685,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>155</v>
+        <v>259</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10694,7 +10709,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10703,7 +10718,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10715,10 +10730,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>196</v>
+        <v>489</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10727,12 +10742,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10746,7 +10761,7 @@
         <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>82</v>
@@ -10755,16 +10770,20 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>108</v>
+        <v>510</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10788,13 +10807,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>82</v>
+        <v>514</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>515</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10812,7 +10831,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>110</v>
+        <v>509</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10821,10 +10840,10 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>82</v>
+        <v>516</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10833,10 +10852,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>111</v>
+        <v>517</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10847,21 +10866,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10873,17 +10892,15 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10920,31 +10937,31 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10967,14 +10984,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10990,23 +11007,21 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>280</v>
+        <v>115</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>281</v>
+        <v>116</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11042,19 +11057,19 @@
         <v>82</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>284</v>
+        <v>121</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11066,7 +11081,7 @@
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11075,10 +11090,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>286</v>
+        <v>111</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11089,10 +11104,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11103,7 +11118,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11112,19 +11127,23 @@
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>108</v>
+        <v>285</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N72" s="2"/>
-      <c r="O72" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11172,19 +11191,19 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>110</v>
+        <v>289</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11193,10 +11212,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>111</v>
+        <v>291</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11207,21 +11226,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -11233,17 +11252,15 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11280,31 +11297,31 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11327,21 +11344,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11350,23 +11367,21 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>293</v>
+        <v>115</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>294</v>
+        <v>116</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11402,31 +11417,31 @@
         <v>82</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>298</v>
+        <v>121</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11435,10 +11450,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>300</v>
+        <v>111</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11449,10 +11464,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11460,7 +11475,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>93</v>
@@ -11475,18 +11490,20 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11534,7 +11551,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11555,10 +11572,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11569,10 +11586,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11580,7 +11597,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>93</v>
@@ -11595,18 +11612,18 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11654,7 +11671,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11675,10 +11692,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11689,10 +11706,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11700,7 +11717,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>93</v>
@@ -11715,17 +11732,17 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11774,7 +11791,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11795,10 +11812,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11809,10 +11826,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11835,19 +11852,17 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>328</v>
+        <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11896,7 +11911,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11917,10 +11932,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11931,10 +11946,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11957,19 +11972,19 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>107</v>
+        <v>333</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -12018,7 +12033,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12039,10 +12054,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12053,21 +12068,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -12076,22 +12091,22 @@
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>262</v>
+        <v>107</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>526</v>
+        <v>343</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>527</v>
+        <v>344</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>528</v>
+        <v>345</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>529</v>
+        <v>346</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12116,11 +12131,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z80" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12138,13 +12155,13 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>524</v>
+        <v>347</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
@@ -12156,31 +12173,31 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>532</v>
+        <v>348</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>533</v>
+        <v>349</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12199,19 +12216,19 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>536</v>
+        <v>267</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>537</v>
+        <v>531</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12236,13 +12253,11 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12260,7 +12275,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12278,27 +12293,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>82</v>
+        <v>539</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12309,7 +12324,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12321,18 +12336,20 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>262</v>
+        <v>541</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>544</v>
       </c>
-      <c r="M82" t="s" s="2">
+      <c r="O82" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N82" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12356,11 +12373,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12378,13 +12397,13 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
@@ -12396,27 +12415,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>548</v>
+        <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>551</v>
+        <v>82</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12439,15 +12458,17 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>108</v>
+        <v>549</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12472,13 +12493,11 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>82</v>
+        <v>552</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12496,7 +12515,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>110</v>
+        <v>548</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12508,44 +12527,44 @@
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>82</v>
+        <v>553</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>82</v>
+        <v>554</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>111</v>
+        <v>555</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>82</v>
+        <v>556</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12557,17 +12576,15 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12604,31 +12621,31 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12651,14 +12668,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12674,23 +12691,21 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>280</v>
+        <v>115</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>281</v>
+        <v>116</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>283</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12726,19 +12741,19 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>284</v>
+        <v>121</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12750,7 +12765,7 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12759,10 +12774,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>285</v>
+        <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>286</v>
+        <v>111</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12773,10 +12788,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12787,7 +12802,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12796,19 +12811,23 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>108</v>
+        <v>285</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>286</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>288</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12856,19 +12875,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>110</v>
+        <v>289</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12877,10 +12896,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>82</v>
+        <v>290</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>111</v>
+        <v>291</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12891,21 +12910,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12917,17 +12936,15 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12964,31 +12981,31 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -13011,21 +13028,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -13034,23 +13051,21 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>293</v>
+        <v>115</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>294</v>
+        <v>116</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -13086,31 +13101,31 @@
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>298</v>
+        <v>121</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -13119,10 +13134,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>300</v>
+        <v>111</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13133,10 +13148,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13144,7 +13159,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>93</v>
@@ -13159,18 +13174,20 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13218,7 +13235,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13239,10 +13256,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13253,10 +13270,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13264,7 +13281,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>93</v>
@@ -13279,18 +13296,18 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13338,7 +13355,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13359,10 +13376,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13373,10 +13390,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13384,7 +13401,7 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>93</v>
@@ -13399,17 +13416,17 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13458,7 +13475,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13479,10 +13496,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13493,10 +13510,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13519,19 +13536,17 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>328</v>
+        <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>331</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13580,7 +13595,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13601,10 +13616,10 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13615,10 +13630,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13641,19 +13656,19 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>107</v>
+        <v>333</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13702,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13723,10 +13738,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13735,12 +13750,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13754,28 +13769,28 @@
         <v>93</v>
       </c>
       <c r="H94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J94" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K94" t="s" s="2">
-        <v>262</v>
+        <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>564</v>
+        <v>343</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>565</v>
+        <v>344</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>566</v>
+        <v>345</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>567</v>
+        <v>346</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13800,11 +13815,13 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y94" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z94" t="s" s="2">
-        <v>568</v>
+        <v>82</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13822,7 +13839,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>563</v>
+        <v>347</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13843,10 +13860,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>569</v>
+        <v>348</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>570</v>
+        <v>349</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13855,12 +13872,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13874,7 +13891,7 @@
         <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>82</v>
@@ -13883,18 +13900,20 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="O95" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="L95" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
       </c>
@@ -13918,13 +13937,11 @@
         <v>82</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>82</v>
+        <v>573</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13942,7 +13959,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13960,27 +13977,27 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
         <v>576</v>
       </c>
-      <c r="AM95" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s" s="2">
-        <v>580</v>
-      </c>
       <c r="B96" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13994,7 +14011,7 @@
         <v>93</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
@@ -14003,16 +14020,16 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14062,7 +14079,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14080,27 +14097,27 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="2">
         <v>585</v>
       </c>
-      <c r="AM96" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>589</v>
-      </c>
       <c r="B97" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14111,10 +14128,10 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>82</v>
@@ -14123,20 +14140,18 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>594</v>
-      </c>
+        <v>589</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14184,45 +14199,45 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>595</v>
+        <v>105</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>82</v>
+        <v>590</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>82</v>
+        <v>593</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14233,7 +14248,7 @@
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
@@ -14245,16 +14260,20 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>107</v>
+        <v>595</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>108</v>
+        <v>596</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>599</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14302,19 +14321,19 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>110</v>
+        <v>594</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>82</v>
+        <v>600</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14323,10 +14342,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>82</v>
+        <v>601</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>111</v>
+        <v>602</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14337,21 +14356,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14363,17 +14382,15 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14422,19 +14439,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14457,14 +14474,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>601</v>
+        <v>113</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14477,26 +14494,24 @@
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>602</v>
+        <v>115</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>603</v>
+        <v>116</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O100" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14544,7 +14559,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>604</v>
+        <v>121</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14568,7 +14583,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14586,26 +14601,26 @@
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>606</v>
+        <v>114</v>
       </c>
       <c r="L101" t="s" s="2">
         <v>607</v>
@@ -14613,8 +14628,12 @@
       <c r="M101" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
+      <c r="N101" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14662,19 +14681,19 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
@@ -14683,10 +14702,10 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>611</v>
+        <v>196</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14697,10 +14716,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14723,13 +14742,13 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>606</v>
+        <v>611</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14780,7 +14799,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14789,7 +14808,7 @@
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14801,10 +14820,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>610</v>
+        <v>615</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14815,10 +14834,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14841,20 +14860,16 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>262</v>
+        <v>611</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N103" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="O103" t="s" s="2">
-        <v>620</v>
-      </c>
+      <c r="N103" s="2"/>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>82</v>
       </c>
@@ -14878,13 +14893,13 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>622</v>
+        <v>82</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14902,7 +14917,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14911,7 +14926,7 @@
         <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>105</v>
@@ -14920,13 +14935,13 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>623</v>
+        <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>533</v>
+        <v>620</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14937,10 +14952,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14951,7 +14966,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14963,19 +14978,19 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15000,13 +15015,13 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -15024,13 +15039,13 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
@@ -15042,13 +15057,13 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15059,10 +15074,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15073,7 +15088,7 @@
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>82</v>
@@ -15085,17 +15100,19 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="L105" t="s" s="2">
+      <c r="O105" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" t="s" s="2">
-        <v>636</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15120,13 +15137,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>82</v>
+        <v>635</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>82</v>
+        <v>636</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15144,13 +15161,13 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>82</v>
@@ -15162,13 +15179,13 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>82</v>
+        <v>628</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>82</v>
+        <v>629</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>637</v>
+        <v>538</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15179,10 +15196,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15205,7 +15222,7 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>107</v>
+        <v>638</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>639</v>
@@ -15214,7 +15231,9 @@
         <v>640</v>
       </c>
       <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
+      <c r="O106" t="s" s="2">
+        <v>641</v>
+      </c>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15262,7 +15281,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15283,10 +15302,10 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>610</v>
+        <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15297,10 +15316,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15311,7 +15330,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>82</v>
@@ -15320,10 +15339,10 @@
         <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>643</v>
+        <v>107</v>
       </c>
       <c r="L107" t="s" s="2">
         <v>644</v>
@@ -15331,9 +15350,7 @@
       <c r="M107" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="N107" t="s" s="2">
-        <v>646</v>
-      </c>
+      <c r="N107" s="2"/>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15382,13 +15399,13 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
@@ -15403,10 +15420,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>647</v>
+        <v>615</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15417,10 +15434,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15443,16 +15460,16 @@
         <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
+        <v>648</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="L108" t="s" s="2">
+      <c r="N108" t="s" s="2">
         <v>651</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>653</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15502,7 +15519,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15523,24 +15540,24 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="AN108" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
         <v>654</v>
       </c>
-      <c r="AO108" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s" s="2">
-        <v>655</v>
-      </c>
       <c r="B109" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15554,7 +15571,7 @@
         <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>82</v>
@@ -15563,20 +15580,18 @@
         <v>94</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>590</v>
+        <v>655</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>656</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="O109" t="s" s="2">
         <v>658</v>
       </c>
+      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15624,7 +15639,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15636,33 +15651,33 @@
         <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AN109" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="AK109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM109" t="s" s="2">
+      <c r="AO109" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="AN109" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>662</v>
-      </c>
       <c r="B110" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15673,28 +15688,32 @@
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>107</v>
+        <v>595</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>108</v>
+        <v>661</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N110" s="2"/>
-      <c r="O110" s="2"/>
+        <v>661</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="O110" t="s" s="2">
+        <v>663</v>
+      </c>
       <c r="P110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15742,19 +15761,19 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>110</v>
+        <v>660</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>82</v>
+        <v>664</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>82</v>
@@ -15763,10 +15782,10 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>82</v>
+        <v>665</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>111</v>
+        <v>666</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15777,21 +15796,21 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15803,17 +15822,15 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N111" s="2"/>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15862,19 +15879,19 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>82</v>
@@ -15897,14 +15914,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>601</v>
+        <v>113</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15917,26 +15934,24 @@
         <v>82</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>602</v>
+        <v>115</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>603</v>
+        <v>116</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O112" t="s" s="2">
-        <v>220</v>
-      </c>
+      <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
         <v>82</v>
       </c>
@@ -15984,7 +15999,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>604</v>
+        <v>121</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16008,7 +16023,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16017,47 +16032,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H113" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I113" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>262</v>
+        <v>114</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>666</v>
+        <v>607</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>667</v>
+        <v>608</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>668</v>
+        <v>117</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>669</v>
+        <v>225</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16082,13 +16097,13 @@
         <v>82</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -16106,34 +16121,34 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>665</v>
+        <v>609</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>670</v>
+        <v>82</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>355</v>
+        <v>82</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>356</v>
+        <v>196</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>82</v>
@@ -16141,10 +16156,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16152,7 +16167,7 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>93</v>
@@ -16167,19 +16182,19 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>671</v>
+      </c>
+      <c r="M114" t="s" s="2">
         <v>672</v>
       </c>
-      <c r="L114" t="s" s="2">
+      <c r="N114" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="M114" t="s" s="2">
+      <c r="O114" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>442</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16207,10 +16222,10 @@
         <v>155</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>676</v>
+        <v>356</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>677</v>
+        <v>357</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>82</v>
@@ -16228,16 +16243,16 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>678</v>
+        <v>82</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>105</v>
@@ -16246,27 +16261,27 @@
         <v>82</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>447</v>
+        <v>360</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>448</v>
+        <v>361</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16286,22 +16301,22 @@
         <v>82</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>262</v>
+        <v>677</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>508</v>
+        <v>447</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16329,10 +16344,10 @@
         <v>155</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>509</v>
+        <v>681</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>510</v>
+        <v>682</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>82</v>
@@ -16350,7 +16365,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16359,7 +16374,7 @@
         <v>93</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>105</v>
@@ -16368,22 +16383,22 @@
         <v>82</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>82</v>
+        <v>684</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>196</v>
+        <v>452</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>512</v>
+        <v>453</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>82</v>
+        <v>454</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
         <v>685</v>
       </c>
@@ -16392,17 +16407,17 @@
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>82</v>
@@ -16411,19 +16426,19 @@
         <v>82</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>526</v>
+        <v>686</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>527</v>
+        <v>687</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>528</v>
+        <v>688</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>529</v>
+        <v>513</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16451,10 +16466,10 @@
         <v>155</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>686</v>
+        <v>514</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>82</v>
@@ -16478,10 +16493,10 @@
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>82</v>
+        <v>689</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>105</v>
@@ -16490,31 +16505,31 @@
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>532</v>
+        <v>196</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>533</v>
+        <v>517</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16533,19 +16548,19 @@
         <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>83</v>
+        <v>267</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>688</v>
+        <v>531</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>689</v>
+        <v>532</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>593</v>
+        <v>533</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>594</v>
+        <v>534</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16570,13 +16585,13 @@
         <v>82</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>82</v>
+        <v>691</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>82</v>
+        <v>535</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>82</v>
@@ -16594,7 +16609,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16612,23 +16627,145 @@
         <v>82</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>82</v>
+        <v>536</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>596</v>
+        <v>537</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>597</v>
+        <v>538</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP117" t="s" s="2">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP118" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP117">
+  <autoFilter ref="A1:AP118">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16638,7 +16775,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI116">
+  <conditionalFormatting sqref="A2:AI117">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$117</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4549" uniqueCount="695">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4511" uniqueCount="690">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T07:29:03+00:00</t>
+    <t>2026-01-29T14:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -696,22 +696,6 @@
 Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
-    <t>Observation.extension:MesOriginOfData</t>
-  </si>
-  <si>
-    <t>MesOriginOfData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
-</t>
-  </si>
-  <si>
-    <t>Origine de la donnée</t>
-  </si>
-  <si>
-    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
-  </si>
-  <si>
     <t>Observation.modifierExtension</t>
   </si>
   <si>
@@ -1370,7 +1354,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2502,7 +2486,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP118"/>
+  <dimension ref="A1:AP117"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.2265625" customWidth="true" bestFit="true"/>
@@ -2515,7 +2499,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="179.3984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -5075,41 +5059,43 @@
         <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>218</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>219</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="N22" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="M22" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -5157,7 +5143,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5181,7 +5167,7 @@
         <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -5199,7 +5185,7 @@
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5212,25 +5198,23 @@
         <v>82</v>
       </c>
       <c r="I23" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J23" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J23" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K23" t="s" s="2">
-        <v>114</v>
+        <v>223</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5279,7 +5263,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5291,22 +5275,22 @@
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>82</v>
+        <v>227</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>82</v>
+        <v>228</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -5314,14 +5298,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>82</v>
+        <v>232</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5340,17 +5324,17 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
@@ -5399,7 +5383,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5414,19 +5398,19 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>82</v>
@@ -5434,14 +5418,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5460,18 +5444,18 @@
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>241</v>
-      </c>
+        <v>244</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>245</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5519,7 +5503,7 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5534,16 +5518,16 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5552,46 +5536,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J26" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>247</v>
+        <v>173</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>252</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>253</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
@@ -5615,13 +5601,11 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
@@ -5639,13 +5623,13 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -5654,30 +5638,30 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>82</v>
+        <v>260</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5688,31 +5672,31 @@
         <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>173</v>
+        <v>262</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5737,35 +5721,35 @@
         <v>82</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>82</v>
@@ -5774,32 +5758,34 @@
         <v>105</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="AL27" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" hidden="true">
-      <c r="A28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C28" s="2"/>
+      <c r="C28" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5808,7 +5794,7 @@
         <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>94</v>
@@ -5820,19 +5806,19 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
@@ -5860,26 +5846,28 @@
         <v>177</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="AC28" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5903,37 +5891,35 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AO28" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AP28" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="29" hidden="true">
+      <c r="A29" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>275</v>
       </c>
-      <c r="AO28" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>277</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="C29" t="s" s="2">
-        <v>278</v>
-      </c>
+      <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>82</v>
@@ -5942,20 +5928,16 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>267</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>268</v>
+        <v>108</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>271</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
       </c>
@@ -5979,13 +5961,13 @@
         <v>82</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>272</v>
+        <v>82</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>273</v>
+        <v>82</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>82</v>
@@ -6003,19 +5985,19 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>266</v>
+        <v>110</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -6027,10 +6009,10 @@
         <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>275</v>
+        <v>111</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>276</v>
+        <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -6038,21 +6020,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
@@ -6064,15 +6046,17 @@
         <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N30" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N30" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -6109,31 +6093,31 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6154,46 +6138,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>115</v>
+        <v>280</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>116</v>
+        <v>281</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O31" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6229,19 +6215,19 @@
         <v>82</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>121</v>
+        <v>284</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6253,7 +6239,7 @@
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6262,10 +6248,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>111</v>
+        <v>286</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6274,12 +6260,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6287,35 +6273,31 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>285</v>
+        <v>108</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6363,19 +6345,19 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>289</v>
+        <v>110</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6384,10 +6366,10 @@
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>291</v>
+        <v>111</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>82</v>
@@ -6398,21 +6380,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>82</v>
@@ -6424,15 +6406,17 @@
         <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
@@ -6469,31 +6453,31 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6514,52 +6498,54 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>115</v>
+        <v>293</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>116</v>
+        <v>294</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6589,31 +6575,31 @@
         <v>82</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC34" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>121</v>
+        <v>298</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>82</v>
@@ -6622,10 +6608,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>111</v>
+        <v>300</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6634,12 +6620,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6647,13 +6633,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6662,26 +6648,24 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>302</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6723,7 +6707,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6744,10 +6728,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6756,12 +6740,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6769,13 +6753,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6784,24 +6768,24 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O36" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>82</v>
+        <v>314</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6843,7 +6827,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6864,10 +6848,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6876,12 +6860,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6889,13 +6873,13 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>82</v>
@@ -6904,24 +6888,24 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>319</v>
+        <v>82</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6963,7 +6947,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6984,10 +6968,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6998,10 +6982,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7024,17 +7008,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>328</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="O38" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7083,7 +7069,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7104,10 +7090,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7118,10 +7104,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7144,19 +7130,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7205,7 +7191,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7226,10 +7212,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -7238,26 +7224,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
@@ -7266,19 +7252,19 @@
         <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>107</v>
+        <v>262</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
@@ -7303,13 +7289,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7327,10 +7313,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>93</v>
@@ -7342,66 +7328,62 @@
         <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>358</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>267</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>352</v>
+        <v>108</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
       </c>
@@ -7425,13 +7407,13 @@
         <v>82</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>82</v>
@@ -7449,10 +7431,10 @@
         <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>350</v>
+        <v>110</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>93</v>
@@ -7461,44 +7443,44 @@
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>358</v>
+        <v>82</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>360</v>
+        <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>361</v>
+        <v>111</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>363</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>82</v>
@@ -7510,15 +7492,17 @@
         <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N42" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N42" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
@@ -7555,31 +7539,31 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7602,18 +7586,18 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>81</v>
@@ -7625,21 +7609,23 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>115</v>
+        <v>280</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>116</v>
+        <v>281</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O43" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7675,11 +7661,9 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>362</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7687,7 +7671,7 @@
         <v>120</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>121</v>
+        <v>284</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7699,7 +7683,7 @@
         <v>82</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>82</v>
@@ -7708,10 +7692,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>111</v>
+        <v>286</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7722,12 +7706,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>361</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>364</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7736,7 +7722,7 @@
         <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>82</v>
@@ -7751,16 +7737,16 @@
         <v>151</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
@@ -7797,17 +7783,19 @@
         <v>82</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7828,10 +7816,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7842,20 +7830,18 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="C45" t="s" s="2">
-        <v>369</v>
-      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>93</v>
@@ -7867,23 +7853,19 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>285</v>
+        <v>108</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7931,19 +7913,19 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>289</v>
+        <v>110</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7952,10 +7934,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>291</v>
+        <v>111</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7966,21 +7948,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7992,15 +7974,17 @@
         <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
@@ -8037,31 +8021,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -8084,21 +8068,21 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>82</v>
@@ -8107,27 +8091,29 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>115</v>
+        <v>293</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>116</v>
+        <v>294</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>82</v>
+        <v>371</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -8157,31 +8143,31 @@
         <v>82</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>121</v>
+        <v>298</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -8190,10 +8176,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>111</v>
+        <v>300</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8204,10 +8190,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8215,7 +8201,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8230,26 +8216,24 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>376</v>
+        <v>82</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8291,7 +8275,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8312,10 +8296,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8326,10 +8310,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8337,7 +8321,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -8352,24 +8336,24 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8411,7 +8395,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8432,10 +8416,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8446,10 +8430,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8457,7 +8441,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>93</v>
@@ -8472,24 +8456,24 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q50" s="2"/>
       <c r="R50" t="s" s="2">
-        <v>381</v>
+        <v>82</v>
       </c>
       <c r="S50" t="s" s="2">
         <v>82</v>
@@ -8531,7 +8515,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8552,10 +8536,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8566,10 +8550,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8592,17 +8576,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>328</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N51" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="O51" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8651,7 +8637,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8672,10 +8658,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8686,10 +8672,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8712,19 +8698,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8773,7 +8759,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8794,10 +8780,10 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>82</v>
@@ -8806,12 +8792,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8819,13 +8805,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G53" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8834,19 +8820,19 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>107</v>
+        <v>383</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>345</v>
+        <v>386</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
@@ -8895,7 +8881,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>347</v>
+        <v>382</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8910,30 +8896,30 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>82</v>
+        <v>388</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>348</v>
+        <v>389</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>349</v>
+        <v>390</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8941,13 +8927,13 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
@@ -8956,20 +8942,18 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -9017,13 +9001,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -9032,19 +9016,19 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>394</v>
+        <v>355</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -9052,21 +9036,21 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -9078,18 +9062,20 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O55" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -9137,13 +9123,13 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>82</v>
@@ -9152,44 +9138,44 @@
         <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>360</v>
+        <v>406</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9198,19 +9184,19 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
@@ -9259,7 +9245,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9268,50 +9254,50 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>105</v>
+        <v>417</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
@@ -9320,20 +9306,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>416</v>
+        <v>129</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9381,7 +9365,7 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9390,25 +9374,25 @@
         <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>422</v>
+        <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9416,10 +9400,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9430,7 +9414,7 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>82</v>
@@ -9442,18 +9426,18 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>129</v>
+        <v>430</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="O58" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
       </c>
@@ -9501,13 +9485,13 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>82</v>
@@ -9516,19 +9500,19 @@
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>434</v>
       </c>
       <c r="AL58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>82</v>
@@ -9536,10 +9520,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9550,10 +9534,10 @@
         <v>80</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
@@ -9562,17 +9546,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O59" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9609,59 +9595,59 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>443</v>
+      </c>
+      <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>442</v>
+        <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="D60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9682,19 +9668,19 @@
         <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
@@ -9704,7 +9690,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9731,17 +9717,19 @@
         <v>82</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="AC60" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9750,7 +9738,7 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9759,31 +9747,29 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="AN60" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AO60" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP60" t="s" s="2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="AO60" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP60" t="s" s="2">
+      <c r="B61" t="s" s="2">
         <v>454</v>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>456</v>
-      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9795,29 +9781,25 @@
         <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>444</v>
+        <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>445</v>
+        <v>108</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>447</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9826,7 +9808,7 @@
         <v>82</v>
       </c>
       <c r="S61" t="s" s="2">
-        <v>457</v>
+        <v>82</v>
       </c>
       <c r="T61" t="s" s="2">
         <v>82</v>
@@ -9865,7 +9847,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>443</v>
+        <v>110</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9874,47 +9856,47 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>450</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>453</v>
+        <v>111</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9926,15 +9908,17 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9971,31 +9955,31 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -10016,46 +10000,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>114</v>
+        <v>459</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>115</v>
+        <v>460</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>116</v>
+        <v>461</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O63" s="2"/>
+        <v>462</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>463</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10091,31 +10077,31 @@
         <v>82</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>121</v>
+        <v>464</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -10124,10 +10110,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>82</v>
+        <v>465</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>111</v>
+        <v>466</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10136,12 +10122,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10149,39 +10135,39 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>464</v>
+        <v>173</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>467</v>
-      </c>
+        <v>470</v>
+      </c>
+      <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q64" s="2"/>
+      <c r="Q64" t="s" s="2">
+        <v>472</v>
+      </c>
       <c r="R64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10201,13 +10187,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>474</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -10225,7 +10211,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10246,10 +10232,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10258,12 +10244,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10271,39 +10257,37 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q65" t="s" s="2">
-        <v>477</v>
-      </c>
+      <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
         <v>82</v>
       </c>
@@ -10323,13 +10307,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>478</v>
+        <v>82</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>479</v>
+        <v>82</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10347,7 +10331,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10368,10 +10352,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10382,10 +10366,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10408,24 +10392,24 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>82</v>
@@ -10467,7 +10451,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10476,7 +10460,7 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>82</v>
+        <v>493</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10488,10 +10472,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10502,10 +10486,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10528,24 +10512,26 @@
         <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>497</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>498</v>
+      </c>
       <c r="O67" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>82</v>
@@ -10563,13 +10549,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>82</v>
+        <v>500</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10587,7 +10573,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10596,7 +10582,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>498</v>
+        <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10608,10 +10594,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10622,10 +10608,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10633,7 +10619,7 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>93</v>
@@ -10645,22 +10631,22 @@
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>173</v>
+        <v>262</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10685,13 +10671,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>259</v>
+        <v>155</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10709,7 +10695,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10718,7 +10704,7 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>105</v>
@@ -10730,10 +10716,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>489</v>
+        <v>196</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10742,12 +10728,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10761,7 +10747,7 @@
         <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>82</v>
@@ -10770,20 +10756,16 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>267</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>510</v>
+        <v>108</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10807,13 +10789,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>514</v>
+        <v>82</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>515</v>
+        <v>82</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10831,7 +10813,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>509</v>
+        <v>110</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10840,10 +10822,10 @@
         <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>516</v>
+        <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10852,10 +10834,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>517</v>
+        <v>111</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10866,21 +10848,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10892,15 +10874,17 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10937,31 +10921,31 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10984,14 +10968,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11007,21 +10991,23 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>115</v>
+        <v>280</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>116</v>
+        <v>281</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11057,19 +11043,19 @@
         <v>82</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC71" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>121</v>
+        <v>284</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -11081,7 +11067,7 @@
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11090,10 +11076,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>111</v>
+        <v>286</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11104,10 +11090,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11118,7 +11104,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11127,23 +11113,19 @@
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>285</v>
+        <v>108</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
       </c>
@@ -11191,19 +11173,19 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>289</v>
+        <v>110</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11212,10 +11194,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>291</v>
+        <v>111</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11226,21 +11208,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -11252,15 +11234,17 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11297,31 +11281,31 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11344,21 +11328,21 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11367,21 +11351,23 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>115</v>
+        <v>293</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>116</v>
+        <v>294</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11417,31 +11403,31 @@
         <v>82</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>121</v>
+        <v>298</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11450,10 +11436,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>111</v>
+        <v>300</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11464,10 +11450,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11475,7 +11461,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>93</v>
@@ -11490,20 +11476,18 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11551,7 +11535,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11572,10 +11556,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11586,10 +11570,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11597,7 +11581,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>93</v>
@@ -11612,18 +11596,18 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11671,7 +11655,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11692,10 +11676,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11706,10 +11690,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11717,7 +11701,7 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
         <v>93</v>
@@ -11732,17 +11716,17 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11791,7 +11775,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11812,10 +11796,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11826,10 +11810,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11852,17 +11836,19 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>107</v>
+        <v>328</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="O78" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11911,7 +11897,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11932,10 +11918,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11946,10 +11932,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11972,19 +11958,19 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -12033,7 +12019,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -12054,10 +12040,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -12068,21 +12054,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -12091,22 +12077,22 @@
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>107</v>
+        <v>262</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>343</v>
+        <v>526</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>344</v>
+        <v>527</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>345</v>
+        <v>528</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>346</v>
+        <v>529</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12131,13 +12117,11 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12155,13 +12139,13 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>347</v>
+        <v>524</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>82</v>
@@ -12173,31 +12157,31 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>348</v>
+        <v>532</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>349</v>
+        <v>533</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12216,19 +12200,19 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>267</v>
+        <v>536</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -12253,29 +12237,31 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y81" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF81" t="s" s="2">
         <v>535</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>529</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12293,27 +12279,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12324,7 +12310,7 @@
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12336,20 +12322,18 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>541</v>
+        <v>262</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12373,13 +12357,11 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12397,13 +12379,13 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
@@ -12415,27 +12397,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>548</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>82</v>
+        <v>551</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12458,17 +12440,15 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>267</v>
+        <v>107</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>549</v>
+        <v>108</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
@@ -12493,11 +12473,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>552</v>
+        <v>82</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12515,7 +12497,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>548</v>
+        <v>110</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12527,44 +12509,44 @@
         <v>82</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>553</v>
+        <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>554</v>
+        <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>555</v>
+        <v>111</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>556</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12576,15 +12558,17 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>82</v>
@@ -12621,31 +12605,31 @@
         <v>82</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>82</v>
@@ -12668,14 +12652,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12691,21 +12675,23 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>115</v>
+        <v>280</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>116</v>
+        <v>281</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12741,19 +12727,19 @@
         <v>82</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>121</v>
+        <v>284</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12765,7 +12751,7 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
@@ -12774,10 +12760,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>111</v>
+        <v>286</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12788,10 +12774,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12802,7 +12788,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12811,23 +12797,19 @@
         <v>82</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>285</v>
+        <v>108</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12875,19 +12857,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>289</v>
+        <v>110</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12896,10 +12878,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>290</v>
+        <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>291</v>
+        <v>111</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12910,21 +12892,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>560</v>
+        <v>556</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12936,15 +12918,17 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12981,31 +12965,31 @@
         <v>82</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -13028,21 +13012,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -13051,21 +13035,23 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>115</v>
+        <v>293</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>116</v>
+        <v>294</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -13101,31 +13087,31 @@
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>121</v>
+        <v>298</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>82</v>
@@ -13134,10 +13120,10 @@
         <v>82</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>111</v>
+        <v>300</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13148,10 +13134,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13159,7 +13145,7 @@
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>93</v>
@@ -13174,20 +13160,18 @@
         <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>301</v>
-      </c>
+        <v>305</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13235,7 +13219,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13256,10 +13240,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13270,10 +13254,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13281,7 +13265,7 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G90" t="s" s="2">
         <v>93</v>
@@ -13296,18 +13280,18 @@
         <v>94</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13355,7 +13339,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13376,10 +13360,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13390,10 +13374,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13401,7 +13385,7 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>93</v>
@@ -13416,17 +13400,17 @@
         <v>94</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13475,7 +13459,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13496,10 +13480,10 @@
         <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13510,10 +13494,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13536,17 +13520,19 @@
         <v>94</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>328</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="O92" t="s" s="2">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13595,7 +13581,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13616,10 +13602,10 @@
         <v>82</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13630,10 +13616,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13656,19 +13642,19 @@
         <v>94</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>333</v>
+        <v>107</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13717,7 +13703,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13738,10 +13724,10 @@
         <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13750,12 +13736,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13769,28 +13755,28 @@
         <v>93</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>107</v>
+        <v>262</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>343</v>
+        <v>564</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>344</v>
+        <v>565</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>345</v>
+        <v>566</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>346</v>
+        <v>567</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13815,13 +13801,11 @@
         <v>82</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>82</v>
+        <v>568</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>82</v>
@@ -13839,7 +13823,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>347</v>
+        <v>563</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13860,10 +13844,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>348</v>
+        <v>569</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>349</v>
+        <v>570</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13872,12 +13856,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13891,7 +13875,7 @@
         <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>82</v>
@@ -13900,20 +13884,18 @@
         <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>267</v>
+        <v>572</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>572</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
       </c>
@@ -13937,11 +13919,13 @@
         <v>82</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y95" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z95" t="s" s="2">
-        <v>573</v>
+        <v>82</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>82</v>
@@ -13959,7 +13943,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13977,27 +13961,27 @@
         <v>82</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>82</v>
+        <v>576</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>82</v>
+        <v>579</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14011,7 +13995,7 @@
         <v>93</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>82</v>
@@ -14020,16 +14004,16 @@
         <v>82</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14079,7 +14063,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14097,27 +14081,27 @@
         <v>82</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14128,10 +14112,10 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>82</v>
@@ -14140,18 +14124,20 @@
         <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>594</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14199,45 +14185,45 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>105</v>
+        <v>595</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>590</v>
+        <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>593</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14248,7 +14234,7 @@
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>82</v>
@@ -14260,20 +14246,16 @@
         <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>595</v>
+        <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>596</v>
+        <v>108</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>599</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14321,19 +14303,19 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>594</v>
+        <v>110</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>600</v>
+        <v>82</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14342,10 +14324,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>601</v>
+        <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>602</v>
+        <v>111</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14356,21 +14338,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14382,15 +14364,17 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14439,19 +14423,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14474,14 +14458,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>113</v>
+        <v>601</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14494,24 +14478,26 @@
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>115</v>
+        <v>602</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>116</v>
+        <v>603</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14559,7 +14545,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>121</v>
+        <v>604</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14583,7 +14569,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14601,26 +14587,26 @@
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>114</v>
+        <v>606</v>
       </c>
       <c r="L101" t="s" s="2">
         <v>607</v>
@@ -14628,12 +14614,8 @@
       <c r="M101" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="N101" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>225</v>
-      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>82</v>
       </c>
@@ -14681,19 +14663,19 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI101" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="AG101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AJ101" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
@@ -14702,10 +14684,10 @@
         <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>196</v>
+        <v>611</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14716,10 +14698,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14742,13 +14724,13 @@
         <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14799,7 +14781,7 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
@@ -14808,7 +14790,7 @@
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14820,10 +14802,10 @@
         <v>82</v>
       </c>
       <c r="AM102" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="AN102" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14834,10 +14816,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14860,16 +14842,20 @@
         <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>611</v>
+        <v>262</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+      <c r="O103" t="s" s="2">
+        <v>620</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
       </c>
@@ -14893,13 +14879,13 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>82</v>
+        <v>621</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>82</v>
+        <v>622</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14917,7 +14903,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14926,7 +14912,7 @@
         <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>105</v>
@@ -14935,13 +14921,13 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>82</v>
+        <v>623</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>615</v>
+        <v>624</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>620</v>
+        <v>533</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14952,10 +14938,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14966,7 +14952,7 @@
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>82</v>
@@ -14978,19 +14964,19 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -15015,13 +15001,13 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -15039,13 +15025,13 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>82</v>
@@ -15057,13 +15043,13 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>628</v>
+        <v>623</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>629</v>
+        <v>624</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -15074,10 +15060,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15088,7 +15074,7 @@
         <v>80</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>82</v>
@@ -15100,19 +15086,17 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>267</v>
+        <v>633</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>633</v>
-      </c>
+        <v>635</v>
+      </c>
+      <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15137,13 +15121,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>635</v>
+        <v>82</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>636</v>
+        <v>82</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15161,13 +15145,13 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>82</v>
@@ -15179,13 +15163,13 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>628</v>
+        <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>629</v>
+        <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>538</v>
+        <v>637</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -15196,10 +15180,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15222,7 +15206,7 @@
         <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>638</v>
+        <v>107</v>
       </c>
       <c r="L106" t="s" s="2">
         <v>639</v>
@@ -15231,9 +15215,7 @@
         <v>640</v>
       </c>
       <c r="N106" s="2"/>
-      <c r="O106" t="s" s="2">
-        <v>641</v>
-      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15281,7 +15263,7 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15302,10 +15284,10 @@
         <v>82</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>82</v>
+        <v>610</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15316,10 +15298,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15330,7 +15312,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>82</v>
@@ -15339,10 +15321,10 @@
         <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>107</v>
+        <v>643</v>
       </c>
       <c r="L107" t="s" s="2">
         <v>644</v>
@@ -15350,7 +15332,9 @@
       <c r="M107" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="N107" s="2"/>
+      <c r="N107" t="s" s="2">
+        <v>646</v>
+      </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15399,13 +15383,13 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>82</v>
@@ -15420,10 +15404,10 @@
         <v>82</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>615</v>
+        <v>647</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15434,10 +15418,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15460,16 +15444,16 @@
         <v>94</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -15519,7 +15503,7 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
@@ -15540,10 +15524,10 @@
         <v>82</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15552,12 +15536,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15571,7 +15555,7 @@
         <v>81</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>82</v>
@@ -15580,18 +15564,20 @@
         <v>94</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>655</v>
+        <v>590</v>
       </c>
       <c r="L109" t="s" s="2">
         <v>656</v>
       </c>
       <c r="M109" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="N109" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="N109" t="s" s="2">
+      <c r="O109" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>82</v>
       </c>
@@ -15639,7 +15625,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15651,7 +15637,7 @@
         <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>105</v>
+        <v>659</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>82</v>
@@ -15660,10 +15646,10 @@
         <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="AO109" t="s" s="2">
         <v>82</v>
@@ -15672,12 +15658,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15688,32 +15674,28 @@
         <v>80</v>
       </c>
       <c r="G110" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J110" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>595</v>
+        <v>107</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>661</v>
+        <v>108</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>663</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15761,19 +15743,19 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>660</v>
+        <v>110</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH110" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI110" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>664</v>
+        <v>82</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>82</v>
@@ -15782,10 +15764,10 @@
         <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>665</v>
+        <v>82</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>666</v>
+        <v>111</v>
       </c>
       <c r="AO110" t="s" s="2">
         <v>82</v>
@@ -15796,21 +15778,21 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
@@ -15822,15 +15804,17 @@
         <v>82</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N111" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
         <v>82</v>
@@ -15879,19 +15863,19 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK111" t="s" s="2">
         <v>82</v>
@@ -15914,14 +15898,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>113</v>
+        <v>601</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15934,24 +15918,26 @@
         <v>82</v>
       </c>
       <c r="I112" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K112" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>115</v>
+        <v>602</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>116</v>
+        <v>603</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O112" s="2"/>
+      <c r="O112" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="P112" t="s" s="2">
         <v>82</v>
       </c>
@@ -15999,7 +15985,7 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>121</v>
+        <v>604</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -16023,7 +16009,7 @@
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -16032,47 +16018,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>114</v>
+        <v>262</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>607</v>
+        <v>666</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>608</v>
+        <v>667</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>117</v>
+        <v>668</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>225</v>
+        <v>669</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>82</v>
@@ -16097,13 +16083,13 @@
         <v>82</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -16121,34 +16107,34 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>609</v>
+        <v>665</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>82</v>
+        <v>670</v>
       </c>
       <c r="AM113" t="s" s="2">
-        <v>82</v>
+        <v>355</v>
       </c>
       <c r="AN113" t="s" s="2">
-        <v>196</v>
+        <v>356</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
       <c r="AP113" t="s" s="2">
         <v>82</v>
@@ -16156,10 +16142,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -16167,7 +16153,7 @@
       </c>
       <c r="E114" s="2"/>
       <c r="F114" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>93</v>
@@ -16182,19 +16168,19 @@
         <v>94</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>267</v>
+        <v>672</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="N114" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="O114" t="s" s="2">
-        <v>674</v>
+        <v>442</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>82</v>
@@ -16222,10 +16208,10 @@
         <v>155</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>356</v>
+        <v>676</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>357</v>
+        <v>677</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>82</v>
@@ -16243,16 +16229,16 @@
         <v>82</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AG114" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH114" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>82</v>
+        <v>678</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>105</v>
@@ -16261,27 +16247,27 @@
         <v>82</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>360</v>
+        <v>447</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>361</v>
+        <v>448</v>
       </c>
       <c r="AO114" t="s" s="2">
-        <v>362</v>
+        <v>82</v>
       </c>
       <c r="AP114" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16301,22 +16287,22 @@
         <v>82</v>
       </c>
       <c r="J115" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>677</v>
+        <v>262</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>447</v>
+        <v>508</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>82</v>
@@ -16344,10 +16330,10 @@
         <v>155</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>681</v>
+        <v>509</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>682</v>
+        <v>510</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>82</v>
@@ -16365,7 +16351,7 @@
         <v>82</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
@@ -16374,7 +16360,7 @@
         <v>93</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>105</v>
@@ -16383,22 +16369,22 @@
         <v>82</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>684</v>
+        <v>82</v>
       </c>
       <c r="AM115" t="s" s="2">
-        <v>452</v>
+        <v>196</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>453</v>
+        <v>512</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP115" t="s" s="2">
-        <v>454</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
         <v>685</v>
       </c>
@@ -16407,17 +16393,17 @@
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H116" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I116" t="s" s="2">
         <v>82</v>
@@ -16426,19 +16412,19 @@
         <v>82</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>686</v>
+        <v>526</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>687</v>
+        <v>527</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>688</v>
+        <v>528</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>513</v>
+        <v>529</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>82</v>
@@ -16466,10 +16452,10 @@
         <v>155</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>514</v>
+        <v>686</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>82</v>
@@ -16493,10 +16479,10 @@
         <v>80</v>
       </c>
       <c r="AH116" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>689</v>
+        <v>82</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>105</v>
@@ -16505,31 +16491,31 @@
         <v>82</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>196</v>
+        <v>532</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>517</v>
+        <v>533</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP116" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -16548,19 +16534,19 @@
         <v>82</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>267</v>
+        <v>83</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>531</v>
+        <v>688</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>532</v>
+        <v>689</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>533</v>
+        <v>593</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>534</v>
+        <v>594</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>82</v>
@@ -16585,13 +16571,13 @@
         <v>82</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>691</v>
+        <v>82</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>535</v>
+        <v>82</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>82</v>
@@ -16609,7 +16595,7 @@
         <v>82</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16627,145 +16613,23 @@
         <v>82</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>536</v>
+        <v>82</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>537</v>
+        <v>596</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>538</v>
+        <v>597</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP117" t="s" s="2">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="P118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP118" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP118">
+  <autoFilter ref="A1:AP117">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16775,7 +16639,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI117">
+  <conditionalFormatting sqref="A2:AI116">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T14:02:34+00:00</t>
+    <t>2026-01-30T09:35:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T09:35:57+00:00</t>
+    <t>2026-01-30T10:15:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.1</t>
+    <t>3.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:15:26+00:00</t>
+    <t>2026-02-02T08:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:09:27+00:00</t>
+    <t>2026-02-02T08:10:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:10:43+00:00</t>
+    <t>2026-02-02T09:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0-ballot</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:29:40+00:00</t>
+    <t>2026-02-18T12:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T12:52:41+00:00</t>
+    <t>2026-02-23T17:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:17:29+00:00</t>
+    <t>2026-03-18T17:41:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T17:41:07+00:00</t>
+    <t>2026-03-31T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:00:47+00:00</t>
+    <t>2026-05-06T11:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T11:42:59+00:00</t>
+    <t>2026-05-07T07:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:18:48+00:00</t>
+    <t>2026-05-07T07:24:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:24:38+00:00</t>
+    <t>2026-06-09T08:46:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-temperature.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T08:46:34+00:00</t>
+    <t>2026-06-26T10:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
